--- a/artfynd/A 19760-2024 artfynd.xlsx
+++ b/artfynd/A 19760-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,132 +806,6 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Övervakning av utter i Värmlands län - barmarksinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>58164123</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Örsjöberget, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>394066.8898499836</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6733681.031314717</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Dalby</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2016-02-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2016-02-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Öppet vatten, inga spår!</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Vattendrag</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Dan Mangsbo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Emil Skoglund, Elin Kannerby, Helena Björnström, Fredrik Sivertsen, Marcus Mikkelä</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Övervakning av utter i Värmlands län - vinterspårning</t>
         </is>
       </c>
     </row>
